--- a/ig/ch-core/StructureDefinition-ch-core-ext-entry-resource-cross-references.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-ext-entry-resource-cross-references.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
